--- a/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -434,19 +434,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.567768" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="6.282054" customWidth="1"/>
+    <x:col min="3" max="3" width="10.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="20.282054" customWidth="1"/>
+    <x:col min="5" max="5" width="23.567768" customWidth="1"/>
+    <x:col min="6" max="6" width="10.567768" customWidth="1"/>
+    <x:col min="7" max="7" width="10.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -473,130 +470,126 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="A2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:f>A2+$B$2</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="F2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="str">
+      <x:c r="G2" t="str">
         <x:f>IF(C2=F2,"Yes", "No")</x:f>
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="A3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:f>A3+$B$3</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="str">
+      <x:c r="G3" t="str">
         <x:f>IF(C3=F3,"Yes", "No")</x:f>
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="str">
+      <x:c r="C4" t="str">
         <x:f>"Test" &amp; A4 &amp; "R3C2"</x:f>
         <x:v>TestAR3C2</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="E4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="F4" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="str">
+      <x:c r="G4" t="str">
         <x:f>IF(C4=F4,"Yes", "No")</x:f>
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="A6" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:f t="array" ref="B6:B6">A2+A3</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:f t="array" ref="C6:D6">TRANSPOSE(A2:A3)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0">
+      <x:c r="A10">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0">
+      <x:c r="A11">
         <x:f>A2 + A10_R1C1_A10_R1C1</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0">
+      <x:c r="A12">
         <x:f>$A$2 + A10_R1C1_A10_R1C1</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0">
+      <x:c r="A13">
         <x:f>SUM(8:9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0">
+      <x:c r="A14">
         <x:f>SUM(8:9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -437,13 +437,13 @@
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="14.424911" customWidth="1"/>
     <x:col min="2" max="2" width="6.282054" customWidth="1"/>
-    <x:col min="3" max="3" width="10.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="20.282054" customWidth="1"/>
-    <x:col min="5" max="5" width="23.567768" customWidth="1"/>
-    <x:col min="6" max="6" width="10.567768" customWidth="1"/>
-    <x:col min="7" max="7" width="10.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="10.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="19.710625" customWidth="1"/>
+    <x:col min="5" max="5" width="22.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="10.282054" customWidth="1"/>
+    <x:col min="7" max="7" width="10.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">

--- a/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -437,13 +437,13 @@
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.424911" customWidth="1"/>
-    <x:col min="2" max="2" width="6.282054" customWidth="1"/>
-    <x:col min="3" max="3" width="10.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="19.710625" customWidth="1"/>
-    <x:col min="5" max="5" width="22.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="10.282054" customWidth="1"/>
-    <x:col min="7" max="7" width="10.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="14.428571" customWidth="1"/>
+    <x:col min="2" max="2" width="6.285714" customWidth="1"/>
+    <x:col min="3" max="3" width="10.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="19.714286" customWidth="1"/>
+    <x:col min="5" max="5" width="22.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="10.285714" customWidth="1"/>
+    <x:col min="7" max="7" width="10.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
